--- a/public/excel/MasterData.xlsx
+++ b/public/excel/MasterData.xlsx
@@ -100,7 +100,7 @@
     <t>B02</t>
   </si>
   <si>
-    <t>ไข่่ดาว</t>
+    <t>ไข่ดาว</t>
   </si>
   <si>
     <t>B03</t>
